--- a/data/trans_dic/IP2003-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen dientes o muelas empastados</t>
+          <t>Menores que tienen dientes o muelas empastados (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 15,14</t>
+          <t>3,27; 16,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 21,93</t>
+          <t>6,16; 20,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,39; 33,99</t>
+          <t>14,47; 32,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,93; 26,76</t>
+          <t>10,59; 26,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,34; 25,6</t>
+          <t>8,46; 25,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,87; 33,08</t>
+          <t>14,6; 32,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 15,83</t>
+          <t>3,46; 15,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,8; 27,51</t>
+          <t>10,68; 27,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 17,24</t>
+          <t>7,01; 17,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,51; 24,04</t>
+          <t>12,12; 24,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,19; 21,59</t>
+          <t>10,4; 20,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,12; 24,17</t>
+          <t>12,84; 24,53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,57; 38,17</t>
+          <t>22,98; 37,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 20,13</t>
+          <t>8,57; 19,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,44; 21,36</t>
+          <t>9,57; 21,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,6; 72,58</t>
+          <t>29,22; 73,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 31,83</t>
+          <t>17,88; 32,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 16,13</t>
+          <t>6,15; 16,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,26; 27,14</t>
+          <t>14,47; 27,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,31; 38,11</t>
+          <t>19,43; 39,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,49; 32,67</t>
+          <t>22,19; 32,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 16,14</t>
+          <t>8,32; 15,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,22; 22,46</t>
+          <t>13,79; 23,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,25; 55,52</t>
+          <t>27,8; 60,49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 24,92</t>
+          <t>9,01; 25,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 16,66</t>
+          <t>5,14; 17,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 15,71</t>
+          <t>2,58; 16,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 13,34</t>
+          <t>3,09; 13,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 17,8</t>
+          <t>5,62; 16,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 17,85</t>
+          <t>5,87; 18,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 12,33</t>
+          <t>2,19; 12,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 16,92</t>
+          <t>4,23; 16,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 18,18</t>
+          <t>9,07; 18,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,72; 15,17</t>
+          <t>6,67; 15,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,35</t>
+          <t>3,18; 11,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 12,84</t>
+          <t>4,62; 12,8</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,75; 28,66</t>
+          <t>12,91; 27,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,73; 33,46</t>
+          <t>16,74; 34,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 35,57</t>
+          <t>18,72; 37,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 22,66</t>
+          <t>5,85; 21,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 19,19</t>
+          <t>6,43; 19,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 20,6</t>
+          <t>7,43; 20,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,49; 31,93</t>
+          <t>15,25; 32,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,59; 57,81</t>
+          <t>8,23; 60,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,42; 20,83</t>
+          <t>11,77; 21,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,82; 24,01</t>
+          <t>14,2; 24,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,56; 31,04</t>
+          <t>19,43; 31,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 38,86</t>
+          <t>10,01; 38,99</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,64; 38,75</t>
+          <t>16,48; 38,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,6; 38,27</t>
+          <t>15,91; 39,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 18,16</t>
+          <t>3,12; 16,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 15,54</t>
+          <t>2,68; 15,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,75; 31,22</t>
+          <t>10,2; 30,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,95; 31,88</t>
+          <t>12,32; 32,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 27,87</t>
+          <t>9,06; 28,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 22,44</t>
+          <t>5,47; 21,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,29; 29,72</t>
+          <t>15,58; 30,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,84; 32,0</t>
+          <t>15,87; 30,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 19,85</t>
+          <t>7,32; 19,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 16,99</t>
+          <t>5,91; 16,7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 22,19</t>
+          <t>6,62; 22,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,09; 34,43</t>
+          <t>14,0; 34,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,44; 21,39</t>
+          <t>4,82; 20,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,88</t>
+          <t>1,16; 11,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 11,95</t>
+          <t>2,15; 12,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,81; 27,81</t>
+          <t>10,21; 27,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 19,07</t>
+          <t>4,39; 18,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,61</t>
+          <t>1,36; 11,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,44; 13,85</t>
+          <t>5,39; 14,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,2; 26,67</t>
+          <t>14,09; 26,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,27; 17,07</t>
+          <t>6,22; 17,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 8,87</t>
+          <t>1,89; 8,71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,87; 17,34</t>
+          <t>7,73; 17,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,96; 21,14</t>
+          <t>10,23; 20,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,88</t>
+          <t>4,33; 12,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,54; 21,18</t>
+          <t>9,51; 20,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,83; 14,13</t>
+          <t>5,44; 14,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,51; 15,7</t>
+          <t>6,28; 14,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 13,45</t>
+          <t>5,41; 13,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,67; 18,04</t>
+          <t>8,44; 18,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,42; 13,7</t>
+          <t>7,54; 14,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,53; 16,7</t>
+          <t>9,36; 16,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 11,45</t>
+          <t>5,58; 11,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,49</t>
+          <t>10,0; 17,19</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,85; 21,86</t>
+          <t>12,15; 21,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,57; 22,32</t>
+          <t>12,44; 22,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,6; 17,83</t>
+          <t>8,79; 17,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,12</t>
+          <t>2,4; 8,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,54; 20,61</t>
+          <t>11,92; 20,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,77; 16,04</t>
+          <t>8,0; 16,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,88; 16,03</t>
+          <t>8,19; 16,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,88</t>
+          <t>1,64; 8,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,81; 20,0</t>
+          <t>13,35; 20,04</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,0; 17,23</t>
+          <t>10,93; 16,99</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,55; 15,39</t>
+          <t>9,36; 15,42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,06</t>
+          <t>2,48; 6,74</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,19; 19,93</t>
+          <t>15,33; 20,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,38; 19,21</t>
+          <t>14,54; 19,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,24; 15,73</t>
+          <t>11,29; 15,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,76; 28,55</t>
+          <t>12,71; 29,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,22; 16,33</t>
+          <t>12,35; 16,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,44</t>
+          <t>11,25; 15,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,05; 15,14</t>
+          <t>11,14; 15,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,46; 18,73</t>
+          <t>11,39; 18,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,28; 17,45</t>
+          <t>14,33; 17,5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13,3; 16,49</t>
+          <t>13,37; 16,52</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,75; 14,83</t>
+          <t>11,82; 14,87</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,05; 21,88</t>
+          <t>12,91; 21,3</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen dientes o muelas empastados (tasa de respuesta: 99,85%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3617</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6668</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12512</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12711</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8319</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13657</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4844</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>13834</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>11936</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>20324</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17356</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>26545</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1578; 7868</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3355; 11072</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7926; 17993</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7719; 19223</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4570; 13908</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8871; 19617</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2108; 9412</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8223; 20993</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>7173; 17453</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>13960; 27721</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12046; 24188</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>19243; 36766</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>28709</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12810</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14845</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>59482</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25612</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10436</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>21422</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>34659</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>54321</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23246</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>36267</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>94142</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>21786; 35877</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8223; 19051</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9478; 21452</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36709; 91881</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>18865; 34038</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6188; 16115</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>15495; 29153</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>24217; 48753</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>44450; 65184</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>16358; 31239</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>28419; 47653</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>69573; 151406</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10213</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6177</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4250</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3999</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6862</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7238</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3705</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>17076</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13415</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7955</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>9688</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>5767; 16118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3230; 11006</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1578; 10014</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1753; 7575</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3740; 10716</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3898; 11960</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1446; 8109</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2774; 10793</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>11845; 23922</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8619; 20049</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4042; 14424</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5657; 15665</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>14002</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18048</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19514</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8448</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9131</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10775</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>17924</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>18301</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>23133</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>28823</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>37438</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>26749</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>9123; 19504</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12310; 25009</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13624; 27000</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4048; 14658</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4906; 14779</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5906; 16646</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>11861; 25283</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>6202; 45394</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>17298; 31245</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>21730; 37613</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>29241; 47118</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>14468; 56375</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>10322</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10613</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9376</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>7221</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5077</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>18199</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19989</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>10550</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>7741</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>6575; 15304</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6659; 16678</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1278; 6675</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>915; 5300</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4359; 12880</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5575; 14553</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3860; 12071</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2226; 8872</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>12878; 24792</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13826; 26516</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6112; 16680</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4426; 12508</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11281</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5728</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3109</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>9425</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5483</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2604</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>10145</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>20707</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>11211</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4419</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>3533; 12099</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>6870; 16847</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2467; 10627</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>508; 5054</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1229; 6942</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>5677; 15137</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2369; 10175</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>738; 6199</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>5960; 16004</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>14748; 28247</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>6539; 18097</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1856; 8544</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>14620</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>19418</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9790</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>17755</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>11664</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>13174</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>11779</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>19168</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>26284</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>32592</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>21570</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>36924</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>9522; 21021</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>13044; 26694</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5622; 15958</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>11753; 25269</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6872; 17812</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>8195; 19229</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7241; 18087</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>13068; 29117</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>18816; 35056</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>24158; 42865</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>14706; 30730</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>27842; 47873</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>24785</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>26216</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>18987</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>6173</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>24961</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>18716</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>18523</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>6032</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>49746</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>44931</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>37510</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>12204</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>18327; 33053</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>19610; 35185</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>13093; 25913</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>3113; 11012</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>18623; 32692</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>13176; 26447</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>13011; 25663</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2542; 12522</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>40980; 61534</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>35241; 54758</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>28791; 47443</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>7081; 19209</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>113305</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>111231</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>88955</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>113048</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>92797</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>90901</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>105364</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>210840</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>204028</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>179856</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>218412</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>98898; 129850</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>96409; 127193</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>74365; 103934</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>83378; 192532</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>84568; 112638</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>79135; 109947</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>78067; 107974</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>85121; 138824</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>190643; 232740</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>182712; 225701</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>160639; 202155</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>181128; 298933</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2003-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 16,31</t>
+          <t>2,78; 15,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 20,34</t>
+          <t>6,11; 20,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,47; 32,84</t>
+          <t>14,8; 34,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 26,38</t>
+          <t>10,46; 26,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,46; 25,74</t>
+          <t>8,44; 25,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 32,28</t>
+          <t>14,85; 32,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 15,43</t>
+          <t>3,45; 15,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,68; 27,26</t>
+          <t>10,97; 27,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 17,07</t>
+          <t>7,21; 17,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,12; 24,06</t>
+          <t>12,25; 24,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,4; 20,89</t>
+          <t>10,03; 21,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,84; 24,53</t>
+          <t>12,41; 24,02</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,98; 37,84</t>
+          <t>23,26; 38,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 19,85</t>
+          <t>8,09; 19,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 21,66</t>
+          <t>9,73; 21,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,22; 73,15</t>
+          <t>29,91; 72,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,88; 32,26</t>
+          <t>18,15; 31,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 16,01</t>
+          <t>6,54; 16,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,47; 27,22</t>
+          <t>13,91; 27,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,43; 39,11</t>
+          <t>19,69; 38,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,19; 32,54</t>
+          <t>22,33; 32,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,32; 15,89</t>
+          <t>8,67; 16,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,79; 23,12</t>
+          <t>13,62; 22,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,8; 60,49</t>
+          <t>27,1; 55,35</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 25,18</t>
+          <t>10,0; 25,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 17,53</t>
+          <t>5,03; 17,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 16,38</t>
+          <t>2,65; 15,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 13,34</t>
+          <t>3,01; 13,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 16,1</t>
+          <t>5,63; 16,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 18,01</t>
+          <t>5,91; 18,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 12,3</t>
+          <t>2,17; 12,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 16,46</t>
+          <t>3,88; 16,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 18,32</t>
+          <t>8,94; 18,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 15,52</t>
+          <t>6,69; 15,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,35</t>
+          <t>3,23; 11,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 12,8</t>
+          <t>4,45; 12,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,91; 27,6</t>
+          <t>13,53; 28,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,74; 34,0</t>
+          <t>16,94; 34,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 37,11</t>
+          <t>18,6; 36,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 21,17</t>
+          <t>5,57; 21,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 19,36</t>
+          <t>6,49; 19,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 20,95</t>
+          <t>8,29; 20,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,25; 32,51</t>
+          <t>15,93; 31,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 60,23</t>
+          <t>8,48; 57,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,77; 21,25</t>
+          <t>11,35; 21,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,2; 24,58</t>
+          <t>13,76; 24,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,43; 31,3</t>
+          <t>18,91; 30,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 38,99</t>
+          <t>10,27; 40,4</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,48; 38,35</t>
+          <t>14,95; 38,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,91; 39,84</t>
+          <t>15,61; 38,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 16,3</t>
+          <t>3,21; 18,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 15,5</t>
+          <t>3,5; 15,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 30,14</t>
+          <t>10,35; 29,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 32,17</t>
+          <t>11,1; 31,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,06; 28,35</t>
+          <t>9,29; 28,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 21,79</t>
+          <t>5,4; 21,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,58; 30,0</t>
+          <t>15,5; 29,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,87; 30,44</t>
+          <t>15,79; 30,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 19,97</t>
+          <t>7,18; 18,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 16,7</t>
+          <t>5,8; 16,28</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,62; 22,66</t>
+          <t>6,5; 22,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,0; 34,33</t>
+          <t>14,14; 34,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 20,79</t>
+          <t>4,77; 20,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,51</t>
+          <t>1,16; 11,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,16</t>
+          <t>2,13; 11,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,21; 27,21</t>
+          <t>9,25; 25,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 18,87</t>
+          <t>4,42; 18,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,45</t>
+          <t>1,27; 10,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,39; 14,48</t>
+          <t>5,39; 14,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,09; 26,98</t>
+          <t>14,05; 27,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 17,23</t>
+          <t>6,52; 18,1</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,71</t>
+          <t>1,92; 8,52</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,73; 17,07</t>
+          <t>7,63; 17,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,23; 20,93</t>
+          <t>10,56; 21,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 12,29</t>
+          <t>3,89; 11,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,51; 20,45</t>
+          <t>9,6; 20,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,44; 14,09</t>
+          <t>5,56; 14,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,28; 14,73</t>
+          <t>6,49; 14,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 13,52</t>
+          <t>5,17; 13,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,44; 18,8</t>
+          <t>7,99; 17,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,54; 14,05</t>
+          <t>7,78; 13,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,36; 16,61</t>
+          <t>9,65; 16,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,58; 11,66</t>
+          <t>5,65; 11,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,0; 17,19</t>
+          <t>9,9; 17,39</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,15; 21,91</t>
+          <t>12,25; 21,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,44; 22,32</t>
+          <t>12,32; 22,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,79; 17,4</t>
+          <t>8,89; 17,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,48</t>
+          <t>2,57; 9,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,92; 20,93</t>
+          <t>11,77; 20,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,0; 16,06</t>
+          <t>7,86; 15,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,19; 16,16</t>
+          <t>7,68; 15,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,07</t>
+          <t>1,63; 7,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,35; 20,04</t>
+          <t>13,08; 19,82</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,93; 16,99</t>
+          <t>11,04; 17,24</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,36; 15,42</t>
+          <t>9,36; 15,06</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,74</t>
+          <t>2,6; 6,84</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,33; 20,13</t>
+          <t>15,26; 20,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,54; 19,19</t>
+          <t>14,58; 19,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,78</t>
+          <t>11,23; 15,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,71; 29,35</t>
+          <t>12,97; 29,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,35; 16,45</t>
+          <t>12,25; 16,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,63</t>
+          <t>11,34; 15,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,14; 15,41</t>
+          <t>11,07; 15,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,39; 18,57</t>
+          <t>11,3; 19,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,33; 17,5</t>
+          <t>14,33; 17,38</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13,37; 16,52</t>
+          <t>13,36; 16,48</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,82; 14,87</t>
+          <t>11,67; 14,78</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,91; 21,3</t>
+          <t>12,88; 21,61</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1578; 7868</t>
+          <t>1341; 7677</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3355; 11072</t>
+          <t>3325; 11052</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7926; 17993</t>
+          <t>8109; 18682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7719; 19223</t>
+          <t>7618; 19283</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4570; 13908</t>
+          <t>4561; 14016</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8871; 19617</t>
+          <t>9023; 19590</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2108; 9412</t>
+          <t>2104; 9571</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8223; 20993</t>
+          <t>8449; 21412</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7173; 17453</t>
+          <t>7368; 18274</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13960; 27721</t>
+          <t>14109; 27707</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12046; 24188</t>
+          <t>11617; 24552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19243; 36766</t>
+          <t>18604; 36004</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21786; 35877</t>
+          <t>22056; 36169</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8223; 19051</t>
+          <t>7762; 18858</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9478; 21452</t>
+          <t>9638; 21534</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36709; 91881</t>
+          <t>37574; 90756</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18865; 34038</t>
+          <t>19147; 33431</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6188; 16115</t>
+          <t>6585; 16534</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15495; 29153</t>
+          <t>14894; 29266</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24217; 48753</t>
+          <t>24544; 48588</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44450; 65184</t>
+          <t>44731; 64396</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16358; 31239</t>
+          <t>17048; 31813</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28419; 47653</t>
+          <t>28077; 46375</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69573; 151406</t>
+          <t>67828; 138536</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5767; 16118</t>
+          <t>6401; 16067</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3230; 11006</t>
+          <t>3157; 10915</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1578; 10014</t>
+          <t>1617; 9205</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1753; 7575</t>
+          <t>1712; 7661</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3740; 10716</t>
+          <t>3750; 11227</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3898; 11960</t>
+          <t>3922; 11973</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1446; 8109</t>
+          <t>1430; 8016</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2774; 10793</t>
+          <t>2544; 10671</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11845; 23922</t>
+          <t>11673; 24452</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8619; 20049</t>
+          <t>8647; 19744</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4042; 14424</t>
+          <t>4100; 14097</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5657; 15665</t>
+          <t>5450; 15105</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9123; 19504</t>
+          <t>9562; 20478</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12310; 25009</t>
+          <t>12459; 25399</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13624; 27000</t>
+          <t>13536; 26689</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4048; 14658</t>
+          <t>3854; 14689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4906; 14779</t>
+          <t>4954; 14761</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5906; 16646</t>
+          <t>6585; 16541</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11861; 25283</t>
+          <t>12390; 24297</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6202; 45394</t>
+          <t>6395; 43526</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17298; 31245</t>
+          <t>16680; 31084</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21730; 37613</t>
+          <t>21056; 37214</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29241; 47118</t>
+          <t>28469; 46398</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14468; 56375</t>
+          <t>14849; 58420</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6575; 15304</t>
+          <t>5967; 15212</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6659; 16678</t>
+          <t>6533; 16067</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1278; 6675</t>
+          <t>1315; 7441</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>915; 5300</t>
+          <t>1197; 5429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4359; 12880</t>
+          <t>4422; 12627</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5575; 14553</t>
+          <t>5024; 14441</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3860; 12071</t>
+          <t>3955; 11993</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2226; 8872</t>
+          <t>2200; 8752</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12878; 24792</t>
+          <t>12808; 24560</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13826; 26516</t>
+          <t>13753; 26615</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6112; 16680</t>
+          <t>5997; 15692</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4426; 12508</t>
+          <t>4344; 12196</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3533; 12099</t>
+          <t>3472; 12196</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6870; 16847</t>
+          <t>6940; 16708</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2467; 10627</t>
+          <t>2438; 10621</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>508; 5054</t>
+          <t>509; 4933</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1229; 6942</t>
+          <t>1214; 6349</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5677; 15137</t>
+          <t>5148; 14293</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2369; 10175</t>
+          <t>2383; 10209</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>738; 6199</t>
+          <t>690; 5839</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5960; 16004</t>
+          <t>5961; 15524</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14748; 28247</t>
+          <t>14714; 28589</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6539; 18097</t>
+          <t>6848; 19010</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1856; 8544</t>
+          <t>1883; 8353</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9522; 21021</t>
+          <t>9400; 21027</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13044; 26694</t>
+          <t>13474; 26981</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5622; 15958</t>
+          <t>5050; 15398</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11753; 25269</t>
+          <t>11858; 24909</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6872; 17812</t>
+          <t>7024; 18011</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8195; 19229</t>
+          <t>8470; 19314</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7241; 18087</t>
+          <t>6924; 17511</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13068; 29117</t>
+          <t>12373; 27352</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18816; 35056</t>
+          <t>19414; 34895</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24158; 42865</t>
+          <t>24915; 43226</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14706; 30730</t>
+          <t>14883; 29647</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27842; 47873</t>
+          <t>27568; 48432</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18327; 33053</t>
+          <t>18478; 32938</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19610; 35185</t>
+          <t>19416; 34903</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13093; 25913</t>
+          <t>13237; 26129</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3113; 11012</t>
+          <t>3334; 11785</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18623; 32692</t>
+          <t>18377; 32732</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13176; 26447</t>
+          <t>12943; 26081</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13011; 25663</t>
+          <t>12194; 25133</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2542; 12522</t>
+          <t>2523; 11916</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>40980; 61534</t>
+          <t>40163; 60852</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>35241; 54758</t>
+          <t>35571; 55584</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28791; 47443</t>
+          <t>28794; 46344</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7081; 19209</t>
+          <t>7402; 19494</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>98898; 129850</t>
+          <t>98461; 130729</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>96409; 127193</t>
+          <t>96632; 128679</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>74365; 103934</t>
+          <t>73987; 105283</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>83378; 192532</t>
+          <t>85095; 196712</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>84568; 112638</t>
+          <t>83875; 112949</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>79135; 109947</t>
+          <t>79780; 109427</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>78067; 107974</t>
+          <t>77560; 108202</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>85121; 138824</t>
+          <t>84499; 142608</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>190643; 232740</t>
+          <t>190555; 231108</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>182712; 225701</t>
+          <t>182534; 225112</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>160639; 202155</t>
+          <t>158663; 200926</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>181128; 298933</t>
+          <t>180719; 303305</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2003-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,4%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22,47%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,94%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,5%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>12,25%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>22,84%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 15,92</t>
+          <t>8,34; 25,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 20,3</t>
+          <t>14,87; 33,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,8; 34,1</t>
+          <t>3,45; 15,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,46; 26,46</t>
+          <t>10,36; 26,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 25,94</t>
+          <t>2,63; 15,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 32,23</t>
+          <t>6,69; 21,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 15,69</t>
+          <t>14,39; 33,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,97; 27,81</t>
+          <t>14,06; 29,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 17,87</t>
+          <t>7,15; 17,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 24,05</t>
+          <t>12,51; 24,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,03; 21,2</t>
+          <t>10,19; 21,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,41; 24,02</t>
+          <t>13,79; 25,47</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28,2%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>30,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>13,35%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>14,99%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>47,35%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,26; 38,15</t>
+          <t>18,48; 31,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,09; 19,65</t>
+          <t>6,29; 16,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 21,74</t>
+          <t>14,26; 27,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,91; 72,25</t>
+          <t>20,46; 38,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,15; 31,68</t>
+          <t>23,57; 38,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 16,43</t>
+          <t>8,4; 20,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,91; 27,33</t>
+          <t>9,44; 21,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,69; 38,97</t>
+          <t>26,17; 42,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,33; 32,14</t>
+          <t>22,49; 32,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 16,18</t>
+          <t>8,61; 16,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,62; 22,5</t>
+          <t>13,22; 22,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,1; 55,35</t>
+          <t>24,99; 37,49</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,9%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>15,96%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,84%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,95%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,31%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 25,1</t>
+          <t>5,6; 17,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 17,38</t>
+          <t>5,82; 17,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 15,06</t>
+          <t>2,19; 12,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 13,49</t>
+          <t>4,13; 16,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 16,87</t>
+          <t>9,39; 24,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,91; 18,03</t>
+          <t>4,72; 16,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 12,16</t>
+          <t>2,66; 15,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 16,28</t>
+          <t>3,03; 14,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,94; 18,73</t>
+          <t>8,55; 18,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 15,28</t>
+          <t>6,72; 15,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,09</t>
+          <t>3,21; 11,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 12,34</t>
+          <t>4,73; 12,83</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23,05%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22,8%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>19,82%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>24,54%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>26,82%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 28,98</t>
+          <t>7,15; 19,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,94; 34,53</t>
+          <t>8,21; 20,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,6; 36,68</t>
+          <t>15,49; 31,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 21,22</t>
+          <t>8,75; 54,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 19,33</t>
+          <t>12,75; 28,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,29; 20,81</t>
+          <t>16,73; 33,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,93; 31,24</t>
+          <t>18,72; 35,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,48; 57,75</t>
+          <t>6,4; 23,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 21,14</t>
+          <t>11,42; 20,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,76; 24,32</t>
+          <t>13,82; 24,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 30,82</t>
+          <t>19,56; 31,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 40,4</t>
+          <t>9,66; 34,65</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20,72%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>25,87%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>25,35%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>8,13%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,96%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,95; 38,12</t>
+          <t>9,75; 31,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,61; 38,38</t>
+          <t>11,95; 31,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 18,17</t>
+          <t>9,24; 27,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 15,88</t>
+          <t>5,87; 23,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,35; 29,54</t>
+          <t>15,64; 38,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,1; 31,92</t>
+          <t>15,6; 38,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,29; 28,17</t>
+          <t>3,15; 18,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 21,49</t>
+          <t>2,82; 15,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,5; 29,72</t>
+          <t>15,29; 29,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,79; 30,56</t>
+          <t>15,84; 32,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 18,78</t>
+          <t>7,58; 19,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 16,28</t>
+          <t>6,13; 16,84</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>13,18%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>22,99%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>11,2%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,5; 22,84</t>
+          <t>2,14; 11,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,14; 34,05</t>
+          <t>9,81; 27,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,77; 20,77</t>
+          <t>4,35; 19,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,23</t>
+          <t>1,37; 11,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,13; 11,12</t>
+          <t>6,93; 22,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,25; 25,7</t>
+          <t>15,09; 34,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,42; 18,93</t>
+          <t>4,44; 21,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,78</t>
+          <t>1,33; 11,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,39; 14,05</t>
+          <t>5,44; 13,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,05; 27,31</t>
+          <t>14,2; 26,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 18,1</t>
+          <t>6,27; 17,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 8,52</t>
+          <t>1,78; 9,05</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,23%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12,95%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>11,87%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>15,23%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>7,54%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>14,37%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 17,07</t>
+          <t>5,83; 14,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,56; 21,15</t>
+          <t>6,51; 15,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 11,86</t>
+          <t>5,01; 13,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 20,16</t>
+          <t>8,12; 18,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,56; 14,25</t>
+          <t>7,87; 17,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,49; 14,79</t>
+          <t>9,96; 21,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,17; 13,09</t>
+          <t>4,33; 11,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,99; 17,66</t>
+          <t>9,94; 21,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,78; 13,98</t>
+          <t>7,42; 13,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,65; 16,75</t>
+          <t>9,53; 16,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,25</t>
+          <t>5,64; 11,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,9; 17,39</t>
+          <t>10,54; 18,31</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>15,98%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>16,43%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>12,75%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>12,25; 21,83</t>
+          <t>11,54; 20,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,32; 22,14</t>
+          <t>7,77; 16,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,89; 17,55</t>
+          <t>7,88; 16,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,07</t>
+          <t>1,36; 7,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,77; 20,96</t>
+          <t>11,85; 21,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,86; 15,84</t>
+          <t>12,57; 22,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,68; 15,83</t>
+          <t>8,6; 17,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,68</t>
+          <t>2,26; 8,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,08; 19,82</t>
+          <t>12,81; 20,0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,04; 17,24</t>
+          <t>11,0; 17,23</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9,36; 15,06</t>
+          <t>9,55; 15,39</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,84</t>
+          <t>2,44; 7,01</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>17,57%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>16,78%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>13,51%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,26; 20,27</t>
+          <t>12,22; 16,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,58; 19,41</t>
+          <t>11,29; 15,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,23; 15,99</t>
+          <t>11,05; 15,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,97; 29,98</t>
+          <t>11,22; 18,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,25; 16,49</t>
+          <t>15,19; 19,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,34; 15,56</t>
+          <t>14,38; 19,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,07; 15,44</t>
+          <t>11,24; 15,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,3; 19,08</t>
+          <t>11,91; 16,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,33; 17,38</t>
+          <t>14,28; 17,45</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13,36; 16,48</t>
+          <t>13,3; 16,49</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,67; 14,78</t>
+          <t>11,75; 14,83</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,88; 21,61</t>
+          <t>12,21; 16,31</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8319</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13657</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4844</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10608</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3617</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6668</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>12512</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12711</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8319</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>13657</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4844</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26545</t>
+          <t>22459</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1341; 7677</t>
+          <t>4506; 13835</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3325; 11052</t>
+          <t>9034; 20103</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8109; 18682</t>
+          <t>2107; 9657</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7618; 19283</t>
+          <t>6448; 16243</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4561; 14016</t>
+          <t>1269; 7302</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9023; 19590</t>
+          <t>3645; 11938</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2104; 9571</t>
+          <t>7884; 18622</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8449; 21412</t>
+          <t>7891; 16763</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7368; 18274</t>
+          <t>7315; 17632</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14109; 27707</t>
+          <t>14415; 27696</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11617; 24552</t>
+          <t>11803; 24996</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18604; 36004</t>
+          <t>16324; 30157</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25612</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10436</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21422</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32030</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>28709</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12810</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>14845</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>59482</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25612</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10436</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>21422</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34659</t>
+          <t>33821</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94142</t>
+          <t>65850</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22056; 36169</t>
+          <t>19504; 33584</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7762; 18858</t>
+          <t>6334; 16237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9638; 21534</t>
+          <t>15272; 29058</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37574; 90756</t>
+          <t>23233; 43463</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19147; 33431</t>
+          <t>22344; 36193</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6585; 16534</t>
+          <t>8064; 19322</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14894; 29266</t>
+          <t>9348; 21157</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24544; 48588</t>
+          <t>26041; 42680</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44731; 64396</t>
+          <t>45048; 65448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17048; 31813</t>
+          <t>16920; 31734</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28077; 46375</t>
+          <t>27258; 46285</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67828; 138536</t>
+          <t>53242; 79873</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6862</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7238</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3705</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5023</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>10213</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6177</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4250</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3999</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6862</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7238</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3705</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9025</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6401; 16067</t>
+          <t>3729; 11848</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3157; 10915</t>
+          <t>3864; 11859</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1617; 9205</t>
+          <t>1445; 8132</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1712; 7661</t>
+          <t>2397; 9747</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3750; 11227</t>
+          <t>6009; 15949</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3922; 11973</t>
+          <t>2962; 10465</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1430; 8016</t>
+          <t>1623; 9604</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2544; 10671</t>
+          <t>1676; 7769</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11673; 24452</t>
+          <t>11165; 23742</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8647; 19744</t>
+          <t>8677; 19604</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4100; 14097</t>
+          <t>4081; 14426</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5450; 15105</t>
+          <t>5357; 14538</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9131</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10775</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17924</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15921</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>14002</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>18048</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>19514</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8448</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9131</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10775</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17924</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18301</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>24694</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9562; 20478</t>
+          <t>5457; 14653</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12459; 25399</t>
+          <t>6524; 16375</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13536; 26689</t>
+          <t>12046; 24832</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3854; 14689</t>
+          <t>6109; 38069</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4954; 14761</t>
+          <t>9008; 20250</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6585; 16541</t>
+          <t>12307; 24611</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12390; 24297</t>
+          <t>13623; 25884</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6395; 43526</t>
+          <t>4485; 16144</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16680; 31084</t>
+          <t>16790; 30625</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21056; 37214</t>
+          <t>21155; 36741</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28469; 46398</t>
+          <t>29443; 46722</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14849; 58420</t>
+          <t>13514; 48479</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9376</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7221</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>10322</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>10613</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>3328</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2664</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7877</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9376</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>7221</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7857</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5967; 15212</t>
+          <t>4167; 13342</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6533; 16067</t>
+          <t>5405; 14424</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1315; 7441</t>
+          <t>3933; 11865</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1197; 5429</t>
+          <t>2323; 9292</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4422; 12627</t>
+          <t>6239; 15464</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5024; 14441</t>
+          <t>6529; 16017</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3955; 11993</t>
+          <t>1290; 7438</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2200; 8752</t>
+          <t>997; 5414</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12808; 24560</t>
+          <t>12632; 24562</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13753; 26615</t>
+          <t>13800; 27869</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5997; 15692</t>
+          <t>6332; 16585</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4344; 12196</t>
+          <t>4591; 12621</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3109</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9425</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5483</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>7037</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>11281</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>5728</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1815</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3109</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9425</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5483</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4128</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3472; 12196</t>
+          <t>1219; 6824</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6940; 16708</t>
+          <t>5457; 15467</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2438; 10621</t>
+          <t>2343; 10283</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>509; 4933</t>
+          <t>653; 5431</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1214; 6349</t>
+          <t>3699; 11847</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5148; 14293</t>
+          <t>7406; 16896</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2383; 10209</t>
+          <t>2270; 10935</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>690; 5839</t>
+          <t>588; 5139</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5961; 15524</t>
+          <t>6012; 15304</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14714; 28589</t>
+          <t>14865; 27924</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6848; 19010</t>
+          <t>6588; 17933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1883; 8353</t>
+          <t>1635; 8301</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>11664</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13174</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>11779</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>14620</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>19418</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>9790</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>17755</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>11664</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>13174</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>11779</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>19168</t>
+          <t>18295</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36924</t>
+          <t>36476</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9400; 21027</t>
+          <t>7371; 17854</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13474; 26981</t>
+          <t>8499; 20502</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5050; 15398</t>
+          <t>6703; 17996</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11858; 24909</t>
+          <t>11398; 26633</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7024; 18011</t>
+          <t>9695; 21361</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8470; 19314</t>
+          <t>12698; 26963</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6924; 17511</t>
+          <t>5620; 15423</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12373; 27352</t>
+          <t>12054; 26241</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19414; 34895</t>
+          <t>18506; 34193</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24915; 43226</t>
+          <t>24594; 43109</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14883; 29647</t>
+          <t>14881; 30195</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27568; 48432</t>
+          <t>27577; 47898</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>24961</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>18716</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>18523</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5838</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>24785</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>26216</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>18987</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>6173</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>24961</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>18716</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>18523</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>12001</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18478; 32938</t>
+          <t>18028; 32190</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19416; 34903</t>
+          <t>12794; 26411</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13237; 26129</t>
+          <t>12511; 25454</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3334; 11785</t>
+          <t>2154; 12103</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>18377; 32732</t>
+          <t>17881; 32975</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12943; 26081</t>
+          <t>19814; 35188</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12194; 25133</t>
+          <t>12806; 26554</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2523; 11916</t>
+          <t>3140; 12231</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>40163; 60852</t>
+          <t>39332; 61417</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>35571; 55584</t>
+          <t>35456; 55531</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28794; 46344</t>
+          <t>29399; 47374</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7402; 19494</t>
+          <t>7239; 20818</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>120</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>92797</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>90901</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>94910</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>113305</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>111231</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>88955</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>113048</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>97535</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>92797</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>90901</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>105364</t>
+          <t>87580</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>218412</t>
+          <t>182490</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>98461; 130729</t>
+          <t>83687; 111819</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>96632; 128679</t>
+          <t>79432; 108594</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>73987; 105283</t>
+          <t>77447; 106142</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>85095; 196712</t>
+          <t>77347; 124939</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>83875; 112949</t>
+          <t>97996; 128552</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>79780; 109427</t>
+          <t>95300; 127320</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77560; 108202</t>
+          <t>73998; 103586</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>84499; 142608</t>
+          <t>73954; 103379</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>190555; 231108</t>
+          <t>189962; 232012</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>182534; 225112</t>
+          <t>181667; 225261</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>158663; 200926</t>
+          <t>159691; 201619</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>180719; 303305</t>
+          <t>159899; 213725</t>
         </is>
       </c>
     </row>
